--- a/import-specification/devices/power-plant-controller.xlsx
+++ b/import-specification/devices/power-plant-controller.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="121">
   <si>
     <t>Field Type</t>
   </si>
@@ -366,6 +366,18 @@
   </si>
   <si>
     <t>Global power plant controller state conditions</t>
+  </si>
+  <si>
+    <t>QS_TX</t>
+  </si>
+  <si>
+    <t>Telegrams transmitted (communication quality)</t>
+  </si>
+  <si>
+    <t>QS_RX</t>
+  </si>
+  <si>
+    <t>Telegrams received (communication quality)</t>
   </si>
 </sst>
 </file>
@@ -717,7 +729,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="16.425" bestFit="true" customWidth="true" style="0"/>
@@ -1424,6 +1436,28 @@
         <v>116</v>
       </c>
     </row>
+    <row r="48" spans="1:8">
+      <c r="A48" t="s">
+        <v>38</v>
+      </c>
+      <c r="B48" t="s">
+        <v>117</v>
+      </c>
+      <c r="D48" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" t="s">
+        <v>38</v>
+      </c>
+      <c r="B49" t="s">
+        <v>119</v>
+      </c>
+      <c r="D49" t="s">
+        <v>120</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
